--- a/jogos_2025-05-26.xlsx
+++ b/jogos_2025-05-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="193">
   <si>
     <t>Date</t>
   </si>
@@ -271,21 +271,21 @@
     <t>Algeria Ligue 1</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Turkey Süper Lig</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
@@ -349,27 +349,27 @@
     <t>US Biskra</t>
   </si>
   <si>
+    <t>Umeå</t>
+  </si>
+  <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
     <t>Hatayspor</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Umeå</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
     <t>Brage</t>
   </si>
   <si>
@@ -385,33 +385,33 @@
     <t>BATE</t>
   </si>
   <si>
+    <t>Al Ittifaq</t>
+  </si>
+  <si>
+    <t>Al Riyadh</t>
+  </si>
+  <si>
+    <t>Al Fateh</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Al Khaleej</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Al Orubah</t>
+  </si>
+  <si>
+    <t>Al Hilal</t>
+  </si>
+  <si>
     <t>Al Raed</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
-    <t>Al Ittifaq</t>
-  </si>
-  <si>
-    <t>Al Orubah</t>
-  </si>
-  <si>
-    <t>Al Riyadh</t>
-  </si>
-  <si>
-    <t>Al Hilal</t>
-  </si>
-  <si>
-    <t>Al Khaleej</t>
-  </si>
-  <si>
     <t>Frosinone</t>
   </si>
   <si>
@@ -421,24 +421,24 @@
     <t>Sportivo Ameliano</t>
   </si>
   <si>
+    <t>Deportivo Recoleta</t>
+  </si>
+  <si>
     <t>Criciúma</t>
   </si>
   <si>
-    <t>Deportivo Recoleta</t>
-  </si>
-  <si>
     <t>Brusque</t>
   </si>
   <si>
     <t>Guarani</t>
   </si>
   <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Quilmes</t>
   </si>
   <si>
@@ -478,27 +478,27 @@
     <t>MC Oran</t>
   </si>
   <si>
+    <t>Örgryte</t>
+  </si>
+  <si>
+    <t>Hartberg</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>Fenerbahçe</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Örgryte</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Hartberg</t>
-  </si>
-  <si>
     <t>Utsikten</t>
   </si>
   <si>
@@ -514,33 +514,33 @@
     <t>Smorgon</t>
   </si>
   <si>
+    <t>Al Wahda</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Al Nassr</t>
+  </si>
+  <si>
+    <t>Dhamk</t>
+  </si>
+  <si>
+    <t>Al Akhdoud</t>
+  </si>
+  <si>
+    <t>Al Shabab</t>
+  </si>
+  <si>
+    <t>Al Taawon</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
     <t>Al Kholood</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
-    <t>Dhamk</t>
-  </si>
-  <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
-    <t>Al Wahda</t>
-  </si>
-  <si>
-    <t>Al Taawon</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Al Akhdoud</t>
-  </si>
-  <si>
     <t>Salernitana</t>
   </si>
   <si>
@@ -550,24 +550,24 @@
     <t>Atlético Tembetary</t>
   </si>
   <si>
+    <t>Sportivo Trinidense</t>
+  </si>
+  <si>
     <t>Coritiba</t>
   </si>
   <si>
-    <t>Sportivo Trinidense</t>
-  </si>
-  <si>
     <t>São Bernardo</t>
   </si>
   <si>
     <t>Figueirense</t>
   </si>
   <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>CRB</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
     <t>San Martín Tucumán</t>
   </si>
   <si>
@@ -577,13 +577,22 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
     <t>suspended</t>
   </si>
   <si>
+    <t>['3', '12', '86']</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['66']</t>
   </si>
 </sst>
 </file>
@@ -1140,13 +1149,13 @@
         <v>144</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1155,100 +1164,100 @@
         <v>187</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AK2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1263,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW2">
         <v>0</v>
@@ -1281,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" s="3">
         <v>45803.16666666666</v>
@@ -1313,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1325,124 +1334,124 @@
         <v>187</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1451,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD3" s="3">
         <v>45803.1875</v>
@@ -1492,16 +1501,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L4">
-        <v>4.44</v>
+        <v>4.7</v>
       </c>
       <c r="M4">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N4">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O4">
         <v>3.5</v>
@@ -1513,106 +1522,106 @@
         <v>1.44</v>
       </c>
       <c r="R4">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T4">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U4">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z4">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AA4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB4">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC4">
         <v>1.67</v>
       </c>
       <c r="AD4">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AE4">
         <v>1.25</v>
       </c>
       <c r="AF4">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH4">
-        <v>6.7</v>
+        <v>6.45</v>
       </c>
       <c r="AI4">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL4">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="AM4">
         <v>1.22</v>
       </c>
       <c r="AN4">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AO4">
         <v>-1</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1662,127 +1671,127 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AO5">
         <v>-1</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1791,10 +1800,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BD5" s="3">
         <v>45803.35416666666</v>
@@ -1832,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L6">
         <v>2.98</v>
@@ -1856,13 +1865,13 @@
         <v>1.38</v>
       </c>
       <c r="S6">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T6">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V6">
         <v>6.5</v>
@@ -1871,49 +1880,49 @@
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AA6">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AB6">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD6">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AE6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AI6">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL6">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AM6">
         <v>1.31</v>
@@ -1925,34 +1934,34 @@
         <v>-1</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -2002,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L7">
         <v>2.33</v>
@@ -2050,7 +2059,7 @@
         <v>1.55</v>
       </c>
       <c r="AA7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB7">
         <v>2.25</v>
@@ -2077,10 +2086,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL7">
         <v>1.5</v>
@@ -2172,16 +2181,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L8">
         <v>1.73</v>
       </c>
       <c r="M8">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N8">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O8">
         <v>1.59</v>
@@ -2193,34 +2202,34 @@
         <v>2.75</v>
       </c>
       <c r="R8">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S8">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W8">
         <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Z8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AA8">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AB8">
         <v>2.1</v>
@@ -2229,16 +2238,16 @@
         <v>1.67</v>
       </c>
       <c r="AD8">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AE8">
         <v>1.25</v>
       </c>
       <c r="AF8">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AH8">
         <v>7</v>
@@ -2247,52 +2256,52 @@
         <v>1.08</v>
       </c>
       <c r="AJ8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL8">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AM8">
         <v>1.28</v>
       </c>
       <c r="AN8">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AQ8">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AR8">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="AS8">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AT8">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AU8">
         <v>2.38</v>
       </c>
       <c r="AV8">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AW8">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AX8">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AY8">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2342,16 +2351,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="M9">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N9">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="O9">
         <v>2.25</v>
@@ -2363,46 +2372,46 @@
         <v>1.81</v>
       </c>
       <c r="R9">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S9">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U9">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AA9">
         <v>3</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD9">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AE9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF9">
         <v>1.85</v>
@@ -2411,58 +2420,58 @@
         <v>1.85</v>
       </c>
       <c r="AH9">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AI9">
         <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL9">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AM9">
         <v>1.28</v>
       </c>
       <c r="AN9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AO9">
         <v>-1</v>
       </c>
       <c r="AP9">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AQ9">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AR9">
         <v>2.65</v>
       </c>
       <c r="AS9">
-        <v>2.65</v>
+        <v>3.34</v>
       </c>
       <c r="AT9">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU9">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AV9">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AW9">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AX9">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AY9">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -2512,94 +2521,94 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO10">
         <v>-1</v>
@@ -2641,10 +2650,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD10" s="3">
         <v>45803.5</v>
@@ -2682,127 +2691,127 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2811,10 +2820,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BD11" s="3">
         <v>45803.57291666666</v>
@@ -2831,7 +2840,7 @@
         <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>111</v>
@@ -2852,127 +2861,127 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L12">
-        <v>9.59</v>
+        <v>2.68</v>
       </c>
       <c r="M12">
-        <v>7.03</v>
+        <v>3.45</v>
       </c>
       <c r="N12">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="O12">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="P12">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q12">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="R12">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="S12">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="U12">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="V12">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="W12">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Z12">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AA12">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB12">
+        <v>1.61</v>
+      </c>
+      <c r="AC12">
+        <v>2.05</v>
+      </c>
+      <c r="AD12">
+        <v>2.8</v>
+      </c>
+      <c r="AE12">
+        <v>1.44</v>
+      </c>
+      <c r="AF12">
+        <v>1.57</v>
+      </c>
+      <c r="AG12">
+        <v>2.2</v>
+      </c>
+      <c r="AH12">
+        <v>5.25</v>
+      </c>
+      <c r="AI12">
+        <v>1.17</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>191</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>191</v>
+      </c>
+      <c r="AL12">
+        <v>1.7</v>
+      </c>
+      <c r="AM12">
         <v>1.22</v>
       </c>
-      <c r="AC12">
-        <v>4.2</v>
-      </c>
-      <c r="AD12">
-        <v>1.61</v>
-      </c>
-      <c r="AE12">
-        <v>2.15</v>
-      </c>
-      <c r="AF12">
-        <v>1.53</v>
-      </c>
-      <c r="AG12">
-        <v>2.38</v>
-      </c>
-      <c r="AH12">
-        <v>2.35</v>
-      </c>
-      <c r="AI12">
-        <v>1.57</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>189</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>189</v>
-      </c>
-      <c r="AL12">
-        <v>3.8</v>
-      </c>
-      <c r="AM12">
-        <v>1.11</v>
-      </c>
       <c r="AN12">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2981,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="BC12">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="BD12" s="3">
         <v>45803.58333333334</v>
@@ -3001,7 +3010,7 @@
         <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
         <v>112</v>
@@ -3022,139 +3031,139 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L13">
         <v>1.7</v>
       </c>
       <c r="M13">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="N13">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P13">
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="R13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S13">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T13">
         <v>2.5</v>
       </c>
       <c r="U13">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V13">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
         <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z13">
         <v>1.25</v>
       </c>
       <c r="AA13">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AB13">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC13">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AD13">
         <v>3</v>
       </c>
       <c r="AE13">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH13">
         <v>5.75</v>
       </c>
       <c r="AI13">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ13" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK13" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL13">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AM13">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AN13">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AQ13">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AR13">
+        <v>1.88</v>
+      </c>
+      <c r="AS13">
+        <v>2.38</v>
+      </c>
+      <c r="AT13">
+        <v>3.15</v>
+      </c>
+      <c r="AU13">
+        <v>2.9</v>
+      </c>
+      <c r="AV13">
+        <v>2.47</v>
+      </c>
+      <c r="AW13">
+        <v>1.92</v>
+      </c>
+      <c r="AX13">
+        <v>1.56</v>
+      </c>
+      <c r="AY13">
+        <v>1.3</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
         <v>1.58</v>
       </c>
-      <c r="AS13">
-        <v>1.93</v>
-      </c>
-      <c r="AT13">
-        <v>2.4</v>
-      </c>
-      <c r="AU13">
-        <v>3.95</v>
-      </c>
-      <c r="AV13">
-        <v>2.8</v>
-      </c>
-      <c r="AW13">
-        <v>2.18</v>
-      </c>
-      <c r="AX13">
-        <v>1.77</v>
-      </c>
-      <c r="AY13">
-        <v>1.49</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.6</v>
-      </c>
       <c r="BC13">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="BD13" s="3">
         <v>45803.58333333334</v>
@@ -3168,7 +3177,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
         <v>99</v>
@@ -3192,61 +3201,61 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L14">
-        <v>2.56</v>
+        <v>3.02</v>
       </c>
       <c r="M14">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="N14">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="O14">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="P14">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AA14">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AB14">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD14">
         <v>3.65</v>
@@ -3255,7 +3264,7 @@
         <v>1.28</v>
       </c>
       <c r="AF14">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
         <v>1.91</v>
@@ -3264,55 +3273,55 @@
         <v>7</v>
       </c>
       <c r="AI14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL14">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AM14">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AN14">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AS14">
+        <v>1.92</v>
+      </c>
+      <c r="AT14">
+        <v>2.4</v>
+      </c>
+      <c r="AU14">
+        <v>3.95</v>
+      </c>
+      <c r="AV14">
+        <v>2.85</v>
+      </c>
+      <c r="AW14">
         <v>2.18</v>
       </c>
-      <c r="AT14">
-        <v>2.8</v>
-      </c>
-      <c r="AU14">
-        <v>3.3</v>
-      </c>
-      <c r="AV14">
-        <v>2.48</v>
-      </c>
-      <c r="AW14">
-        <v>1.94</v>
-      </c>
       <c r="AX14">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AY14">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3321,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BC14">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BD14" s="3">
         <v>45803.58333333334</v>
@@ -3338,7 +3347,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
         <v>99</v>
@@ -3362,128 +3371,128 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L15">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="M15">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="N15">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="P15">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Q15">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="R15">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S15">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="T15">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="V15">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z15">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AA15">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB15">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AC15">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AD15">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="AE15">
+        <v>1.28</v>
+      </c>
+      <c r="AF15">
+        <v>1.91</v>
+      </c>
+      <c r="AG15">
+        <v>1.91</v>
+      </c>
+      <c r="AH15">
+        <v>7</v>
+      </c>
+      <c r="AI15">
+        <v>1.09</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>191</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>191</v>
+      </c>
+      <c r="AL15">
+        <v>1.49</v>
+      </c>
+      <c r="AM15">
+        <v>1.31</v>
+      </c>
+      <c r="AN15">
         <v>1.44</v>
-      </c>
-      <c r="AF15">
-        <v>1.57</v>
-      </c>
-      <c r="AG15">
-        <v>2.2</v>
-      </c>
-      <c r="AH15">
-        <v>5.25</v>
-      </c>
-      <c r="AI15">
-        <v>1.17</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>189</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>189</v>
-      </c>
-      <c r="AL15">
-        <v>1.7</v>
-      </c>
-      <c r="AM15">
-        <v>1.22</v>
-      </c>
-      <c r="AN15">
-        <v>1.35</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AQ15">
+        <v>1.48</v>
+      </c>
+      <c r="AR15">
+        <v>1.76</v>
+      </c>
+      <c r="AS15">
+        <v>2.18</v>
+      </c>
+      <c r="AT15">
+        <v>2.8</v>
+      </c>
+      <c r="AU15">
+        <v>3.3</v>
+      </c>
+      <c r="AV15">
+        <v>2.48</v>
+      </c>
+      <c r="AW15">
+        <v>1.94</v>
+      </c>
+      <c r="AX15">
+        <v>1.58</v>
+      </c>
+      <c r="AY15">
         <v>1.38</v>
       </c>
-      <c r="AR15">
-        <v>1.61</v>
-      </c>
-      <c r="AS15">
-        <v>1.98</v>
-      </c>
-      <c r="AT15">
-        <v>2.48</v>
-      </c>
-      <c r="AU15">
-        <v>3.8</v>
-      </c>
-      <c r="AV15">
-        <v>2.8</v>
-      </c>
-      <c r="AW15">
-        <v>2.15</v>
-      </c>
-      <c r="AX15">
-        <v>1.73</v>
-      </c>
-      <c r="AY15">
-        <v>1.48</v>
-      </c>
       <c r="AZ15">
         <v>0</v>
       </c>
@@ -3491,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BC15">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BD15" s="3">
         <v>45803.58333333334</v>
@@ -3532,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L16">
         <v>2.67</v>
@@ -3607,10 +3616,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL16">
         <v>1.57</v>
@@ -3678,7 +3687,7 @@
         <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
         <v>99</v>
@@ -3702,94 +3711,94 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L17">
-        <v>3.02</v>
+        <v>1.7</v>
       </c>
       <c r="M17">
-        <v>3.26</v>
+        <v>3.61</v>
       </c>
       <c r="N17">
-        <v>2.08</v>
+        <v>3.96</v>
       </c>
       <c r="O17">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="P17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="R17">
+        <v>1.33</v>
+      </c>
+      <c r="S17">
+        <v>3.1</v>
+      </c>
+      <c r="T17">
+        <v>2.5</v>
+      </c>
+      <c r="U17">
+        <v>1.48</v>
+      </c>
+      <c r="V17">
+        <v>6.35</v>
+      </c>
+      <c r="W17">
+        <v>1.06</v>
+      </c>
+      <c r="X17">
+        <v>1.05</v>
+      </c>
+      <c r="Y17">
+        <v>10</v>
+      </c>
+      <c r="Z17">
+        <v>1.25</v>
+      </c>
+      <c r="AA17">
+        <v>3.95</v>
+      </c>
+      <c r="AB17">
+        <v>1.74</v>
+      </c>
+      <c r="AC17">
+        <v>1.96</v>
+      </c>
+      <c r="AD17">
+        <v>3</v>
+      </c>
+      <c r="AE17">
         <v>1.4</v>
       </c>
-      <c r="S17">
-        <v>2.75</v>
-      </c>
-      <c r="T17">
-        <v>2.88</v>
-      </c>
-      <c r="U17">
-        <v>1.36</v>
-      </c>
-      <c r="V17">
-        <v>7.6</v>
-      </c>
-      <c r="W17">
-        <v>1.03</v>
-      </c>
-      <c r="X17">
-        <v>1.06</v>
-      </c>
-      <c r="Y17">
-        <v>9</v>
-      </c>
-      <c r="Z17">
-        <v>1.33</v>
-      </c>
-      <c r="AA17">
-        <v>3.35</v>
-      </c>
-      <c r="AB17">
-        <v>1.95</v>
-      </c>
-      <c r="AC17">
-        <v>1.75</v>
-      </c>
-      <c r="AD17">
-        <v>3.65</v>
-      </c>
-      <c r="AE17">
-        <v>1.28</v>
-      </c>
       <c r="AF17">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AI17">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL17">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AM17">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AN17">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="AO17">
         <v>-1</v>
@@ -3804,7 +3813,7 @@
         <v>1.58</v>
       </c>
       <c r="AS17">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AT17">
         <v>2.4</v>
@@ -3813,7 +3822,7 @@
         <v>3.95</v>
       </c>
       <c r="AV17">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AW17">
         <v>2.18</v>
@@ -3831,10 +3840,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="BC17">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="BD17" s="3">
         <v>45803.58333333334</v>
@@ -3872,127 +3881,127 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L18">
-        <v>1.7</v>
+        <v>9.59</v>
       </c>
       <c r="M18">
-        <v>3.53</v>
+        <v>7.03</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="O18">
-        <v>1.58</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q18">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="R18">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="S18">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="T18">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="U18">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>6.25</v>
+        <v>3.25</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>9.5</v>
+        <v>29</v>
       </c>
       <c r="Z18">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AA18">
-        <v>3.7</v>
+        <v>8.5</v>
       </c>
       <c r="AB18">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AC18">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="AD18">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="AE18">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="AH18">
-        <v>5.75</v>
+        <v>2.35</v>
       </c>
       <c r="AI18">
-        <v>1.12</v>
+        <v>1.57</v>
       </c>
       <c r="AJ18" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK18" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL18">
-        <v>1.22</v>
+        <v>3.8</v>
       </c>
       <c r="AM18">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AN18">
-        <v>1.98</v>
+        <v>1.07</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AQ18">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AR18">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AS18">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AT18">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AU18">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="AV18">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="AW18">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AX18">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AY18">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -4001,10 +4010,10 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.58</v>
+        <v>3.75</v>
       </c>
       <c r="BC18">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="BD18" s="3">
         <v>45803.58333333334</v>
@@ -4018,7 +4027,7 @@
         <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
         <v>99</v>
@@ -4042,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L19">
         <v>1.75</v>
@@ -4117,10 +4126,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL19">
         <v>1.22</v>
@@ -4212,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L20">
         <v>1.45</v>
@@ -4287,10 +4296,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ20" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK20" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL20">
         <v>1.12</v>
@@ -4382,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L21">
         <v>2</v>
       </c>
       <c r="M21">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O21">
         <v>1.74</v>
@@ -4403,64 +4412,64 @@
         <v>2.19</v>
       </c>
       <c r="R21">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S21">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T21">
         <v>2.5</v>
       </c>
       <c r="U21">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="V21">
         <v>5.75</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AA21">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AB21">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC21">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD21">
-        <v>2.79</v>
+        <v>3.25</v>
       </c>
       <c r="AE21">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AF21">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG21">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH21">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="AI21">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AJ21" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK21" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL21">
         <v>1.3</v>
@@ -4469,40 +4478,40 @@
         <v>1.28</v>
       </c>
       <c r="AN21">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ21">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AS21">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AT21">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AU21">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="AV21">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AW21">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AX21">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AY21">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4552,16 +4561,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L22">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="M22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N22">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O22">
         <v>1.54</v>
@@ -4573,22 +4582,22 @@
         <v>2.6</v>
       </c>
       <c r="R22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S22">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="T22">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U22">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -4597,40 +4606,40 @@
         <v>8.1</v>
       </c>
       <c r="Z22">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AA22">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB22">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC22">
+        <v>1.95</v>
+      </c>
+      <c r="AD22">
+        <v>2.9</v>
+      </c>
+      <c r="AE22">
+        <v>1.38</v>
+      </c>
+      <c r="AF22">
+        <v>1.72</v>
+      </c>
+      <c r="AG22">
         <v>2</v>
       </c>
-      <c r="AD22">
-        <v>2.8</v>
-      </c>
-      <c r="AE22">
-        <v>1.37</v>
-      </c>
-      <c r="AF22">
-        <v>1.71</v>
-      </c>
-      <c r="AG22">
-        <v>2.03</v>
-      </c>
       <c r="AH22">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="AI22">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ22" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK22" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL22">
         <v>1.29</v>
@@ -4639,40 +4648,40 @@
         <v>1.25</v>
       </c>
       <c r="AN22">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AQ22">
         <v>1.62</v>
       </c>
       <c r="AR22">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AS22">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="AT22">
-        <v>3.48</v>
+        <v>3.32</v>
       </c>
       <c r="AU22">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AV22">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AW22">
         <v>1.75</v>
       </c>
       <c r="AX22">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AY22">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4722,16 +4731,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L23">
         <v>1.45</v>
       </c>
       <c r="M23">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N23">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="O23">
         <v>1.39</v>
@@ -4743,73 +4752,73 @@
         <v>3.82</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S23">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="T23">
-        <v>3.18</v>
+        <v>2.61</v>
       </c>
       <c r="U23">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="V23">
-        <v>8.699999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z23">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AA23">
-        <v>2.83</v>
+        <v>3.9</v>
       </c>
       <c r="AB23">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="AC23">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AD23">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="AE23">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AF23">
-        <v>2.52</v>
+        <v>1.85</v>
       </c>
       <c r="AG23">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AH23">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="AI23">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AJ23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AM23">
         <v>1.2</v>
       </c>
       <c r="AN23">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AO23">
         <v>-1</v>
@@ -4892,31 +4901,31 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L24">
-        <v>3.06</v>
+        <v>2.02</v>
       </c>
       <c r="M24">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="N24">
+        <v>3.2</v>
+      </c>
+      <c r="O24">
+        <v>1.73</v>
+      </c>
+      <c r="P24">
+        <v>11.5</v>
+      </c>
+      <c r="Q24">
         <v>2.1</v>
       </c>
-      <c r="O24">
-        <v>2.05</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>1.8</v>
-      </c>
       <c r="R24">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S24">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T24">
         <v>2.5</v>
@@ -4931,88 +4940,88 @@
         <v>1.13</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="AB24">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO24">
         <v>-1</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ24">
         <v>0</v>
@@ -5021,10 +5030,10 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="BC24">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="BD24" s="3">
         <v>45803.625</v>
@@ -5062,127 +5071,127 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L25">
-        <v>4.89</v>
+        <v>6.02</v>
       </c>
       <c r="M25">
-        <v>4.77</v>
+        <v>4.98</v>
       </c>
       <c r="N25">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="O25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q25">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="R25">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S25">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T25">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="U25">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V25">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="W25">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AB25">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AC25">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD25">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AE25">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AF25">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AG25">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO25">
         <v>-1</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -5191,10 +5200,10 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC25">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="BD25" s="3">
         <v>45803.625</v>
@@ -5232,127 +5241,127 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L26">
-        <v>1.34</v>
+        <v>4.89</v>
       </c>
       <c r="M26">
-        <v>5.11</v>
+        <v>4.77</v>
       </c>
       <c r="N26">
-        <v>6.4</v>
+        <v>1.46</v>
       </c>
       <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="P26">
+        <v>21</v>
+      </c>
+      <c r="Q26">
+        <v>1.36</v>
+      </c>
+      <c r="R26">
+        <v>1.17</v>
+      </c>
+      <c r="S26">
+        <v>4.5</v>
+      </c>
+      <c r="T26">
+        <v>1.83</v>
+      </c>
+      <c r="U26">
+        <v>1.83</v>
+      </c>
+      <c r="V26">
+        <v>3.75</v>
+      </c>
+      <c r="W26">
+        <v>1.25</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>20</v>
+      </c>
+      <c r="Z26">
+        <v>1.03</v>
+      </c>
+      <c r="AA26">
+        <v>7.5</v>
+      </c>
+      <c r="AB26">
         <v>1.3</v>
       </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
+      <c r="AC26">
         <v>3.4</v>
       </c>
-      <c r="R26">
-        <v>1.22</v>
-      </c>
-      <c r="S26">
-        <v>4</v>
-      </c>
-      <c r="T26">
-        <v>2.1</v>
-      </c>
-      <c r="U26">
-        <v>1.67</v>
-      </c>
-      <c r="V26">
-        <v>4.33</v>
-      </c>
-      <c r="W26">
-        <v>1.2</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
+      <c r="AD26">
+        <v>1.82</v>
+      </c>
+      <c r="AE26">
+        <v>1.89</v>
+      </c>
+      <c r="AF26">
         <v>1.44</v>
       </c>
-      <c r="AC26">
+      <c r="AG26">
         <v>2.63</v>
       </c>
-      <c r="AD26">
-        <v>2.15</v>
-      </c>
-      <c r="AE26">
-        <v>1.61</v>
-      </c>
-      <c r="AF26">
-        <v>1.67</v>
-      </c>
-      <c r="AG26">
-        <v>2.1</v>
-      </c>
       <c r="AH26">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ26" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK26" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO26">
         <v>-1</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ26">
         <v>0</v>
@@ -5361,10 +5370,10 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="BC26">
-        <v>3.4</v>
+        <v>1.36</v>
       </c>
       <c r="BD26" s="3">
         <v>45803.625</v>
@@ -5402,67 +5411,67 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L27">
-        <v>3.52</v>
+        <v>1.34</v>
       </c>
       <c r="M27">
-        <v>3.62</v>
+        <v>5.11</v>
       </c>
       <c r="N27">
-        <v>1.89</v>
+        <v>6.4</v>
       </c>
       <c r="O27">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q27">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="R27">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S27">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U27">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="AB27">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AC27">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF27">
         <v>1.67</v>
@@ -5471,58 +5480,58 @@
         <v>2.1</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AJ27" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK27" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -5531,10 +5540,10 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="BC27">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="BD27" s="3">
         <v>45803.625</v>
@@ -5572,127 +5581,127 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L28">
-        <v>2.02</v>
+        <v>2.76</v>
       </c>
       <c r="M28">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="N28">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="O28">
+        <v>2.2</v>
+      </c>
+      <c r="P28">
+        <v>10</v>
+      </c>
+      <c r="Q28">
         <v>1.73</v>
       </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>2.1</v>
-      </c>
       <c r="R28">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S28">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T28">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V28">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W28">
+        <v>1.1</v>
+      </c>
+      <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>10.3</v>
+      </c>
+      <c r="Z28">
+        <v>1.25</v>
+      </c>
+      <c r="AA28">
+        <v>3.74</v>
+      </c>
+      <c r="AB28">
+        <v>1.81</v>
+      </c>
+      <c r="AC28">
+        <v>1.9</v>
+      </c>
+      <c r="AD28">
+        <v>3.05</v>
+      </c>
+      <c r="AE28">
+        <v>1.36</v>
+      </c>
+      <c r="AF28">
+        <v>1.73</v>
+      </c>
+      <c r="AG28">
+        <v>2</v>
+      </c>
+      <c r="AH28">
+        <v>5.62</v>
+      </c>
+      <c r="AI28">
         <v>1.13</v>
       </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
+      <c r="AJ28" t="s">
+        <v>191</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>191</v>
+      </c>
+      <c r="AL28">
         <v>1.7</v>
       </c>
-      <c r="AC28">
-        <v>2</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>1.57</v>
-      </c>
-      <c r="AG28">
-        <v>2.25</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>189</v>
-      </c>
-      <c r="AK28" t="s">
-        <v>189</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO28">
         <v>-1</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ28">
         <v>0</v>
@@ -5701,10 +5710,10 @@
         <v>0</v>
       </c>
       <c r="BB28">
+        <v>2.2</v>
+      </c>
+      <c r="BC28">
         <v>1.73</v>
-      </c>
-      <c r="BC28">
-        <v>2.1</v>
       </c>
       <c r="BD28" s="3">
         <v>45803.625</v>
@@ -5742,127 +5751,127 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L29">
-        <v>2.48</v>
+        <v>3.52</v>
       </c>
       <c r="M29">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="N29">
-        <v>2.58</v>
+        <v>1.89</v>
       </c>
       <c r="O29">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P29">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="R29">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S29">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T29">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U29">
+        <v>1.5</v>
+      </c>
+      <c r="V29">
+        <v>6</v>
+      </c>
+      <c r="W29">
+        <v>1.11</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>13</v>
+      </c>
+      <c r="Z29">
+        <v>1.22</v>
+      </c>
+      <c r="AA29">
+        <v>4.01</v>
+      </c>
+      <c r="AB29">
+        <v>1.78</v>
+      </c>
+      <c r="AC29">
+        <v>1.98</v>
+      </c>
+      <c r="AD29">
+        <v>2.68</v>
+      </c>
+      <c r="AE29">
         <v>1.44</v>
       </c>
-      <c r="V29">
-        <v>5.8</v>
-      </c>
-      <c r="W29">
-        <v>1.07</v>
-      </c>
-      <c r="X29">
-        <v>1.05</v>
-      </c>
-      <c r="Y29">
-        <v>9.5</v>
-      </c>
-      <c r="Z29">
-        <v>1.25</v>
-      </c>
-      <c r="AA29">
-        <v>3.75</v>
-      </c>
-      <c r="AB29">
-        <v>1.8</v>
-      </c>
-      <c r="AC29">
-        <v>2</v>
-      </c>
-      <c r="AD29">
-        <v>3</v>
-      </c>
-      <c r="AE29">
-        <v>1.38</v>
-      </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH29">
-        <v>5.75</v>
+        <v>4.78</v>
       </c>
       <c r="AI29">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AJ29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL29">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AM29">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN29">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ29">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AR29">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AS29">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="AT29">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AU29">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="AV29">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AW29">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AX29">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AY29">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5871,10 +5880,10 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BC29">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="BD29" s="3">
         <v>45803.625</v>
@@ -5912,127 +5921,127 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L30">
-        <v>6.02</v>
+        <v>2.48</v>
       </c>
       <c r="M30">
-        <v>4.98</v>
+        <v>3.65</v>
       </c>
       <c r="N30">
-        <v>1.37</v>
+        <v>2.58</v>
       </c>
       <c r="O30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q30">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S30">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="T30">
+        <v>2.6</v>
+      </c>
+      <c r="U30">
+        <v>1.44</v>
+      </c>
+      <c r="V30">
+        <v>5.8</v>
+      </c>
+      <c r="W30">
+        <v>1.07</v>
+      </c>
+      <c r="X30">
+        <v>1.05</v>
+      </c>
+      <c r="Y30">
+        <v>9.5</v>
+      </c>
+      <c r="Z30">
+        <v>1.25</v>
+      </c>
+      <c r="AA30">
+        <v>3.75</v>
+      </c>
+      <c r="AB30">
+        <v>1.8</v>
+      </c>
+      <c r="AC30">
         <v>2</v>
       </c>
-      <c r="U30">
-        <v>1.73</v>
-      </c>
-      <c r="V30">
-        <v>4.33</v>
-      </c>
-      <c r="W30">
-        <v>1.2</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>1.44</v>
-      </c>
-      <c r="AC30">
-        <v>2.63</v>
-      </c>
       <c r="AD30">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AE30">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AF30">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG30">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ30" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK30" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO30">
         <v>-1</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ30">
         <v>0</v>
@@ -6041,10 +6050,10 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC30">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="BD30" s="3">
         <v>45803.625</v>
@@ -6082,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L31">
         <v>1.64</v>
@@ -6097,7 +6106,7 @@
         <v>1.4</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -6121,16 +6130,16 @@
         <v>1.2</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="AB31">
         <v>1.44</v>
@@ -6151,58 +6160,58 @@
         <v>2.38</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AJ31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO31">
         <v>-1</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AZ31">
         <v>0</v>
@@ -6252,127 +6261,127 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L32">
-        <v>2.76</v>
+        <v>3.06</v>
       </c>
       <c r="M32">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="N32">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="O32">
+        <v>2.05</v>
+      </c>
+      <c r="P32">
+        <v>11.5</v>
+      </c>
+      <c r="Q32">
+        <v>1.8</v>
+      </c>
+      <c r="R32">
+        <v>1.33</v>
+      </c>
+      <c r="S32">
+        <v>3.25</v>
+      </c>
+      <c r="T32">
+        <v>2.5</v>
+      </c>
+      <c r="U32">
+        <v>1.5</v>
+      </c>
+      <c r="V32">
+        <v>5.5</v>
+      </c>
+      <c r="W32">
+        <v>1.13</v>
+      </c>
+      <c r="X32">
+        <v>1.03</v>
+      </c>
+      <c r="Y32">
+        <v>11.5</v>
+      </c>
+      <c r="Z32">
+        <v>1.21</v>
+      </c>
+      <c r="AA32">
+        <v>4.28</v>
+      </c>
+      <c r="AB32">
+        <v>1.67</v>
+      </c>
+      <c r="AC32">
+        <v>2.1</v>
+      </c>
+      <c r="AD32">
+        <v>2.68</v>
+      </c>
+      <c r="AE32">
+        <v>1.46</v>
+      </c>
+      <c r="AF32">
+        <v>1.62</v>
+      </c>
+      <c r="AG32">
         <v>2.2</v>
       </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>1.73</v>
-      </c>
-      <c r="R32">
-        <v>1.36</v>
-      </c>
-      <c r="S32">
-        <v>3</v>
-      </c>
-      <c r="T32">
-        <v>2.75</v>
-      </c>
-      <c r="U32">
-        <v>1.4</v>
-      </c>
-      <c r="V32">
-        <v>6.5</v>
-      </c>
-      <c r="W32">
-        <v>1.1</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>1.81</v>
-      </c>
-      <c r="AC32">
-        <v>1.9</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>1.73</v>
-      </c>
-      <c r="AG32">
-        <v>2</v>
-      </c>
       <c r="AH32">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ32" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK32" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO32">
         <v>-1</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ32">
         <v>0</v>
@@ -6381,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="BB32">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="BC32">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BD32" s="3">
         <v>45803.625</v>
@@ -6422,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -6497,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK33" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6592,16 +6601,16 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L34">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M34">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N34">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="O34">
         <v>1.31</v>
@@ -6613,106 +6622,106 @@
         <v>3.64</v>
       </c>
       <c r="R34">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S34">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z34">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AA34">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC34">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AD34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE34">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG34">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH34">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AI34">
         <v>1.06</v>
       </c>
       <c r="AJ34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL34">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM34">
         <v>1.16</v>
       </c>
       <c r="AN34">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="AO34">
         <v>-1</v>
       </c>
       <c r="AP34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AU34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AV34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AW34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AX34">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ34">
         <v>0</v>
@@ -6762,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L35">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="M35">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="N35">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="O35">
         <v>1.82</v>
@@ -6783,28 +6792,28 @@
         <v>2.4</v>
       </c>
       <c r="R35">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S35">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="T35">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="U35">
         <v>1.26</v>
       </c>
       <c r="V35">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z35">
         <v>1.45</v>
@@ -6819,67 +6828,67 @@
         <v>1.5</v>
       </c>
       <c r="AD35">
-        <v>4.92</v>
+        <v>5.1</v>
       </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AG35">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH35">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AI35">
         <v>1.01</v>
       </c>
       <c r="AJ35" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK35" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL35">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AM35">
         <v>1.33</v>
       </c>
       <c r="AN35">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AO35">
         <v>-1</v>
       </c>
       <c r="AP35">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AQ35">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AR35">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="AS35">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AT35">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AU35">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AV35">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AW35">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AX35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY35">
         <v>1.15</v>
@@ -6908,7 +6917,7 @@
         <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
         <v>99</v>
@@ -6932,128 +6941,128 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L36">
-        <v>2.41</v>
+        <v>2.94</v>
       </c>
       <c r="M36">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N36">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="O36">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="P36">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="R36">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="S36">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U36">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V36">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z36">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AA36">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB36">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="AC36">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AD36">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AG36">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AH36">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AI36">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ36" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK36" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AM36">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AN36">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AO36">
         <v>-1</v>
       </c>
       <c r="AP36">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AQ36">
+        <v>1.67</v>
+      </c>
+      <c r="AR36">
+        <v>2.34</v>
+      </c>
+      <c r="AS36">
+        <v>2.7</v>
+      </c>
+      <c r="AT36">
+        <v>3.6</v>
+      </c>
+      <c r="AU36">
+        <v>2.7</v>
+      </c>
+      <c r="AV36">
+        <v>2.1</v>
+      </c>
+      <c r="AW36">
+        <v>1.63</v>
+      </c>
+      <c r="AX36">
+        <v>1.4</v>
+      </c>
+      <c r="AY36">
         <v>1.25</v>
       </c>
-      <c r="AR36">
-        <v>1.57</v>
-      </c>
-      <c r="AS36">
-        <v>1.82</v>
-      </c>
-      <c r="AT36">
-        <v>2.34</v>
-      </c>
-      <c r="AU36">
-        <v>4.35</v>
-      </c>
-      <c r="AV36">
-        <v>3.4</v>
-      </c>
-      <c r="AW36">
-        <v>2.4</v>
-      </c>
-      <c r="AX36">
-        <v>1.83</v>
-      </c>
-      <c r="AY36">
-        <v>1.5</v>
-      </c>
       <c r="AZ36">
         <v>0</v>
       </c>
@@ -7061,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="BB36">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="BC36">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="BD36" s="3">
         <v>45803.79166666666</v>
@@ -7078,7 +7087,7 @@
         <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
         <v>99</v>
@@ -7102,127 +7111,127 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L37">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="M37">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N37">
+        <v>2.73</v>
+      </c>
+      <c r="O37">
+        <v>1.8</v>
+      </c>
+      <c r="P37">
+        <v>5.75</v>
+      </c>
+      <c r="Q37">
+        <v>2.4</v>
+      </c>
+      <c r="R37">
+        <v>1.55</v>
+      </c>
+      <c r="S37">
+        <v>2.3</v>
+      </c>
+      <c r="T37">
+        <v>3.5</v>
+      </c>
+      <c r="U37">
+        <v>1.25</v>
+      </c>
+      <c r="V37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W37">
+        <v>1.02</v>
+      </c>
+      <c r="X37">
+        <v>1.11</v>
+      </c>
+      <c r="Y37">
+        <v>6</v>
+      </c>
+      <c r="Z37">
+        <v>1.53</v>
+      </c>
+      <c r="AA37">
         <v>2.25</v>
       </c>
-      <c r="O37">
-        <v>2.1</v>
-      </c>
-      <c r="P37">
-        <v>8</v>
-      </c>
-      <c r="Q37">
-        <v>2</v>
-      </c>
-      <c r="R37">
+      <c r="AB37">
+        <v>2.34</v>
+      </c>
+      <c r="AC37">
+        <v>1.49</v>
+      </c>
+      <c r="AD37">
+        <v>5</v>
+      </c>
+      <c r="AE37">
+        <v>1.14</v>
+      </c>
+      <c r="AF37">
+        <v>2.15</v>
+      </c>
+      <c r="AG37">
+        <v>1.67</v>
+      </c>
+      <c r="AH37">
+        <v>12</v>
+      </c>
+      <c r="AI37">
+        <v>1.04</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>191</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>191</v>
+      </c>
+      <c r="AL37">
         <v>1.4</v>
       </c>
-      <c r="S37">
-        <v>2.65</v>
-      </c>
-      <c r="T37">
-        <v>3.1</v>
-      </c>
-      <c r="U37">
-        <v>1.35</v>
-      </c>
-      <c r="V37">
-        <v>8</v>
-      </c>
-      <c r="W37">
-        <v>1.07</v>
-      </c>
-      <c r="X37">
-        <v>1.05</v>
-      </c>
-      <c r="Y37">
-        <v>8</v>
-      </c>
-      <c r="Z37">
-        <v>1.33</v>
-      </c>
-      <c r="AA37">
-        <v>3</v>
-      </c>
-      <c r="AB37">
-        <v>2.09</v>
-      </c>
-      <c r="AC37">
-        <v>1.67</v>
-      </c>
-      <c r="AD37">
-        <v>3.6</v>
-      </c>
-      <c r="AE37">
-        <v>1.25</v>
-      </c>
-      <c r="AF37">
-        <v>1.77</v>
-      </c>
-      <c r="AG37">
-        <v>1.85</v>
-      </c>
-      <c r="AH37">
-        <v>7.5</v>
-      </c>
-      <c r="AI37">
-        <v>1.07</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>189</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>189</v>
-      </c>
-      <c r="AL37">
-        <v>1.33</v>
-      </c>
       <c r="AM37">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AN37">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AO37">
         <v>-1</v>
       </c>
       <c r="AP37">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AR37">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="AS37">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="AT37">
-        <v>3.55</v>
+        <v>2.25</v>
       </c>
       <c r="AU37">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AV37">
-        <v>2.12</v>
+        <v>3.07</v>
       </c>
       <c r="AW37">
-        <v>1.63</v>
+        <v>2.32</v>
       </c>
       <c r="AX37">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AY37">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AZ37">
         <v>0</v>
@@ -7231,10 +7240,10 @@
         <v>0</v>
       </c>
       <c r="BB37">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="BC37">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="BD37" s="3">
         <v>45803.79166666666</v>
@@ -7272,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L38">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="M38">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="N38">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="O38">
         <v>1.91</v>
@@ -7293,106 +7302,106 @@
         <v>2.42</v>
       </c>
       <c r="R38">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S38">
-        <v>2.13</v>
+        <v>2.67</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U38">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="W38">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
         <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="Z38">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AA38">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AB38">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AD38">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AE38">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH38">
-        <v>9.25</v>
+        <v>7.5</v>
       </c>
       <c r="AI38">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL38">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AM38">
         <v>1.32</v>
       </c>
       <c r="AN38">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AO38">
         <v>-1</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ38">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR38">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AS38">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AT38">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="AU38">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AV38">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AW38">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AX38">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AY38">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AZ38">
         <v>0</v>
@@ -7442,16 +7451,16 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L39">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="M39">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="N39">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="O39">
         <v>1.71</v>
@@ -7463,106 +7472,106 @@
         <v>2.6</v>
       </c>
       <c r="R39">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S39">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T39">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U39">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V39">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W39">
         <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y39">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="Z39">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AA39">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AB39">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="AC39">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AD39">
-        <v>4.55</v>
+        <v>3.68</v>
       </c>
       <c r="AE39">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG39">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH39">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AI39">
         <v>1.03</v>
       </c>
       <c r="AJ39" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK39" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL39">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AM39">
         <v>1.29</v>
       </c>
       <c r="AN39">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AO39">
         <v>-1</v>
       </c>
       <c r="AP39">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR39">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AS39">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AT39">
+        <v>2.4</v>
+      </c>
+      <c r="AU39">
+        <v>4</v>
+      </c>
+      <c r="AV39">
+        <v>2.9</v>
+      </c>
+      <c r="AW39">
         <v>2.25</v>
       </c>
-      <c r="AU39">
-        <v>4.1</v>
-      </c>
-      <c r="AV39">
-        <v>2.95</v>
-      </c>
-      <c r="AW39">
-        <v>2.55</v>
-      </c>
       <c r="AX39">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AY39">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AZ39">
         <v>0</v>
@@ -7588,7 +7597,7 @@
         <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
         <v>99</v>
@@ -7612,127 +7621,127 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L40">
-        <v>2.34</v>
+        <v>1.4</v>
       </c>
       <c r="M40">
-        <v>2.93</v>
+        <v>4.74</v>
       </c>
       <c r="N40">
-        <v>2.84</v>
+        <v>7</v>
       </c>
       <c r="O40">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="P40">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="Q40">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R40">
+        <v>1.33</v>
+      </c>
+      <c r="S40">
+        <v>3.2</v>
+      </c>
+      <c r="T40">
+        <v>2.5</v>
+      </c>
+      <c r="U40">
         <v>1.5</v>
       </c>
-      <c r="S40">
-        <v>2.4</v>
-      </c>
-      <c r="T40">
-        <v>3.4</v>
-      </c>
-      <c r="U40">
-        <v>1.29</v>
-      </c>
       <c r="V40">
-        <v>8.9</v>
+        <v>5.4</v>
       </c>
       <c r="W40">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>6.5</v>
+        <v>14</v>
       </c>
       <c r="Z40">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AA40">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB40">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AC40">
-        <v>1.57</v>
+        <v>2.19</v>
       </c>
       <c r="AD40">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AF40">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG40">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AH40">
-        <v>9.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI40">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AJ40" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK40" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL40">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AM40">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AN40">
-        <v>1.42</v>
+        <v>2.75</v>
       </c>
       <c r="AO40">
         <v>-1</v>
       </c>
       <c r="AP40">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AQ40">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AR40">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AS40">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AT40">
+        <v>2.25</v>
+      </c>
+      <c r="AU40">
+        <v>4.5</v>
+      </c>
+      <c r="AV40">
+        <v>3.2</v>
+      </c>
+      <c r="AW40">
         <v>2.5</v>
       </c>
-      <c r="AU40">
-        <v>3.8</v>
-      </c>
-      <c r="AV40">
-        <v>2.7</v>
-      </c>
-      <c r="AW40">
-        <v>2.12</v>
-      </c>
       <c r="AX40">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AY40">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AZ40">
         <v>0</v>
@@ -7741,10 +7750,10 @@
         <v>0</v>
       </c>
       <c r="BB40">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="BC40">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="BD40" s="3">
         <v>45803.83333333334</v>
@@ -7758,7 +7767,7 @@
         <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
         <v>99</v>
@@ -7782,127 +7791,127 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L41">
-        <v>1.38</v>
+        <v>2.34</v>
       </c>
       <c r="M41">
-        <v>4.25</v>
+        <v>2.93</v>
       </c>
       <c r="N41">
-        <v>6</v>
+        <v>2.84</v>
       </c>
       <c r="O41">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="P41">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="Q41">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="R41">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S41">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="T41">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="U41">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z41">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AA41">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="AB41">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC41">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AD41">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="AE41">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG41">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH41">
-        <v>5</v>
+        <v>9.1</v>
       </c>
       <c r="AI41">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AJ41" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK41" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL41">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AM41">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AN41">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="AO41">
         <v>-1</v>
       </c>
       <c r="AP41">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR41">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AS41">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AT41">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AU41">
-        <v>4.85</v>
+        <v>3.8</v>
       </c>
       <c r="AV41">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AW41">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AX41">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AY41">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AZ41">
         <v>0</v>
@@ -7911,10 +7920,10 @@
         <v>0</v>
       </c>
       <c r="BB41">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="BC41">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="BD41" s="3">
         <v>45803.83333333334</v>
@@ -7952,73 +7961,73 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L42">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M42">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="N42">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O42">
         <v>1.95</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
       </c>
       <c r="R42">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="S42">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T42">
-        <v>4.45</v>
+        <v>4.1</v>
       </c>
       <c r="U42">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="V42">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="W42">
         <v>1.02</v>
       </c>
       <c r="X42">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Y42">
         <v>4.75</v>
       </c>
       <c r="Z42">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA42">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB42">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AC42">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD42">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF42">
         <v>2.5</v>
       </c>
       <c r="AG42">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH42">
         <v>13.5</v>
@@ -8027,52 +8036,52 @@
         <v>1.02</v>
       </c>
       <c r="AJ42" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK42" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL42">
+        <v>1.27</v>
+      </c>
+      <c r="AM42">
         <v>1.41</v>
       </c>
-      <c r="AM42">
-        <v>0</v>
-      </c>
       <c r="AN42">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AO42">
         <v>-1</v>
       </c>
       <c r="AP42">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42">
+        <v>1.91</v>
+      </c>
+      <c r="AR42">
+        <v>2.42</v>
+      </c>
+      <c r="AS42">
+        <v>3.15</v>
+      </c>
+      <c r="AT42">
+        <v>4.4</v>
+      </c>
+      <c r="AU42">
+        <v>2.35</v>
+      </c>
+      <c r="AV42">
         <v>1.84</v>
       </c>
-      <c r="AR42">
-        <v>2.3</v>
-      </c>
-      <c r="AS42">
-        <v>3.14</v>
-      </c>
-      <c r="AT42">
-        <v>4.35</v>
-      </c>
-      <c r="AU42">
-        <v>2.54</v>
-      </c>
-      <c r="AV42">
-        <v>1.81</v>
-      </c>
       <c r="AW42">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AX42">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AY42">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AZ42">
         <v>0</v>
@@ -8122,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L43">
         <v>1.94</v>
@@ -8197,10 +8206,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ43" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK43" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL43">
         <v>1.25</v>
@@ -8292,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L44">
         <v>2.02</v>
@@ -8313,25 +8322,25 @@
         <v>2.88</v>
       </c>
       <c r="R44">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="S44">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="T44">
         <v>3.7</v>
       </c>
       <c r="U44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V44">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="W44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X44">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y44">
         <v>5.75</v>
@@ -8349,31 +8358,31 @@
         <v>1.52</v>
       </c>
       <c r="AD44">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="AE44">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
         <v>2.2</v>
       </c>
       <c r="AG44">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH44">
         <v>13</v>
       </c>
       <c r="AI44">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ44" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK44" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL44">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AM44">
         <v>1.36</v>
@@ -8385,34 +8394,34 @@
         <v>-1</v>
       </c>
       <c r="AP44">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AQ44">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AR44">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AS44">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="AT44">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="AU44">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AV44">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AW44">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AX44">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AY44">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AZ44">
         <v>0</v>

--- a/jogos_2025-05-26.xlsx
+++ b/jogos_2025-05-26.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1690,94 +1690,94 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="P10" t="n">
         <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="X10" t="n">
-        <v>3.23</v>
+        <v>2.78</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45803.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1819,10 +1819,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.33</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC11" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45803.5</v>
@@ -2052,119 +2052,119 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
         <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['21', '64']</t>
+          <t>['47', '66']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '63']</t>
         </is>
       </c>
       <c r="AG13" t="n">
         <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45803.58333333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>5</v>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,49 +2217,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.02</v>
+        <v>2.56</v>
       </c>
       <c r="M14" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
         <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AA14" t="n">
         <v>3.65</v>
@@ -2268,32 +2268,32 @@
         <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
         <v>1.91</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['28', '43', '45+1', '57', '62']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45803.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.04</v>
+        <v>3.61</v>
       </c>
       <c r="N15" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.5</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.96</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AA15" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2409,20 +2409,20 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['19', '42', '55']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.91</v>
+        <v>2.65</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45803.58333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="M16" t="n">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>4.47</v>
       </c>
       <c r="P16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="AB16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.5</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AD16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['38', '43', '83']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['10', '66', '72']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45803.58333333334</v>
@@ -2578,103 +2578,103 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" t="n">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['38', '43', '83']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['10', '66', '72']</t>
+          <t>['28', '43', '45+1', '57', '62']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,35 +2697,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
         <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
         <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['47', '66']</t>
+          <t>['21', '64']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['38', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
         <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45803.58333333334</v>
@@ -2826,35 +2826,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.96</v>
+        <v>9.59</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>7.03</v>
       </c>
       <c r="N19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P19" t="n">
         <v>3.25</v>
       </c>
-      <c r="O19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="S19" t="n">
-        <v>3.42</v>
+        <v>5.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.22</v>
       </c>
-      <c r="X19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.74</v>
-      </c>
       <c r="Z19" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.85</v>
+        <v>1.61</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44', '53', '63', '66']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['19', '42', '55']</t>
+          <t>['27', '90+4']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>3.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45803.58333333334</v>
@@ -2955,32 +2955,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>9.59</v>
+        <v>2.67</v>
       </c>
       <c r="M20" t="n">
-        <v>7.03</v>
+        <v>3.32</v>
       </c>
       <c r="N20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.2</v>
       </c>
-      <c r="O20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="X20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.57</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AH20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI20" t="n">
         <v>2.38</v>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['44', '53', '63', '66']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['27', '90+4']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45803.58333333334</v>
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3249,43 +3249,43 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="M22" t="n">
-        <v>3.47</v>
+        <v>3.11</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>3.06</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="P22" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Y22" t="n">
         <v>1.76</v>
@@ -3294,38 +3294,38 @@
         <v>1.94</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['25', '43', '50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['28', '51', '62', '81']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45803.61458333334</v>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3378,43 +3378,43 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="M23" t="n">
-        <v>3.11</v>
+        <v>3.47</v>
       </c>
       <c r="N23" t="n">
-        <v>3.06</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Y23" t="n">
         <v>1.76</v>
@@ -3423,38 +3423,38 @@
         <v>1.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '43', '50']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['28', '51', '62', '81']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45803.61458333334</v>
@@ -3610,23 +3610,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
@@ -3636,22 +3636,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.64</v>
       </c>
       <c r="M25" t="n">
-        <v>5.11</v>
+        <v>4.11</v>
       </c>
       <c r="N25" t="n">
-        <v>6.4</v>
+        <v>4.15</v>
       </c>
       <c r="O25" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="R25" t="n">
         <v>1.22</v>
@@ -3666,13 +3666,13 @@
         <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>5.84</v>
+        <v>6.38</v>
       </c>
       <c r="Y25" t="n">
         <v>1.44</v>
@@ -3681,20 +3681,20 @@
         <v>2.63</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['25', '69']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45803.625</v>
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD26" t="n">
         <v>2</v>
       </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="O26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X26" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['45+4', '81', '90+6']</t>
+          <t>['47', '60']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['42', '75']</t>
+          <t>['65', '90+5', '90+15']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AI26" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45803.625</v>
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O27" t="n">
+        <v>7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>3.74</v>
+        <v>5.52</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['47', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['65', '90+5', '90+15']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45803.625</v>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,22 +4023,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="M28" t="n">
-        <v>4.11</v>
+        <v>5.11</v>
       </c>
       <c r="N28" t="n">
-        <v>4.15</v>
+        <v>6.4</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R28" t="n">
         <v>1.22</v>
@@ -4053,13 +4053,13 @@
         <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
-        <v>6.38</v>
+        <v>5.84</v>
       </c>
       <c r="Y28" t="n">
         <v>1.44</v>
@@ -4068,20 +4068,20 @@
         <v>2.63</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['25', '69']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45803.625</v>
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>6.02</v>
+        <v>2.48</v>
       </c>
       <c r="M29" t="n">
-        <v>4.98</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>1.37</v>
+        <v>2.58</v>
       </c>
       <c r="O29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="T29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z29" t="n">
         <v>2</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X29" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '40', '86']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['22', '38']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>3.2</v>
+        <v>1.48</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45803.625</v>
@@ -4255,54 +4255,54 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Raed</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.02</v>
+        <v>3.06</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
         <v>2.5</v>
@@ -4311,53 +4311,53 @@
         <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X30" t="n">
-        <v>4.36</v>
+        <v>4.28</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['45', '90+6']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['45+4', '70']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45803.625</v>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.48</v>
+        <v>3.52</v>
       </c>
       <c r="M31" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="N31" t="n">
-        <v>2.58</v>
+        <v>1.89</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.44</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['18', '40', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['22', '38']</t>
+          <t>['9', '85']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI31" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45803.625</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,28 +4539,28 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.52</v>
+        <v>2.02</v>
       </c>
       <c r="M32" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>1.89</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
         <v>2.5</v>
@@ -4569,53 +4569,53 @@
         <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X32" t="n">
-        <v>4.01</v>
+        <v>4.36</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['45', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['9', '85']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45803.625</v>
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Raed</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
         <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.06</v>
+        <v>4.89</v>
       </c>
       <c r="M33" t="n">
-        <v>3.51</v>
+        <v>4.77</v>
       </c>
       <c r="N33" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.03</v>
       </c>
-      <c r="W33" t="n">
-        <v>1.21</v>
-      </c>
       <c r="X33" t="n">
-        <v>4.28</v>
+        <v>7.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.68</v>
+        <v>1.82</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.46</v>
+        <v>1.89</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['45+4', '81', '90+6']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['45+4', '70']</t>
+          <t>['42', '75']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45803.625</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,22 +5029,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U36" t="n">
         <v>1.4</v>
       </c>
-      <c r="M36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['33', '85']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X36" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['17', '4502', '9007']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['42', '67']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>3.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45803.79166666666</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
         <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.05</v>
+        <v>1.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="N38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA38" t="n">
         <v>2.11</v>
       </c>
-      <c r="O38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AB38" t="n">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['17', '4502', '9007']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['33', '85']</t>
+          <t>['42', '67']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.28</v>
+        <v>2.97</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45803.79166666666</v>
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.42</v>
+        <v>1.64</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['11']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AI39" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45803.8125</v>
@@ -5545,22 +5545,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.64</v>
+        <v>2.42</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.45</v>
       </c>
-      <c r="S40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI40" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45803.8125</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,19 +5674,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
         <v>1</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.36</v>
+        <v>2.21</v>
       </c>
       <c r="M41" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>8.1</v>
+        <v>2.9</v>
       </c>
       <c r="O41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['1', '46']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI41" t="n">
         <v>1.91</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['45+4']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ41" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45803.83333333334</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,19 +5803,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.21</v>
+        <v>1.36</v>
       </c>
       <c r="M42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S42" t="n">
         <v>3</v>
       </c>
-      <c r="N42" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.45</v>
-      </c>
       <c r="T42" t="n">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="U42" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V42" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="X42" t="n">
-        <v>2.53</v>
+        <v>3.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.45</v>
+        <v>3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['1', '46']</t>
+          <t>['45+4']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45803.83333333334</v>
